--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tstaarhustech-my.sharepoint.com/personal/mttb_aarhustech_dk/Documents/Dokumenter/!Proj Svendeprøve/Motor Styring/KiCad/Motorcontrol_PCB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="8_{DE797DB4-78F7-4576-8F2B-83C1FBB31666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6810399-652B-42F1-9B0B-AE417453F300}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2D8E87CF-7937-4B28-9774-349BF069D439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{385C476A-CF6B-4484-A9B1-70C264C3616E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{401BF44A-3428-4A7B-AC22-22EE5F407A1A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{401BF44A-3428-4A7B-AC22-22EE5F407A1A}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="2" r:id="rId1"/>
@@ -266,9 +266,6 @@
     <t>R112,R122,R132,R142</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>05.000.0315</t>
   </si>
   <si>
@@ -498,6 +495,9 @@
   </si>
   <si>
     <t>Rotary Encoder</t>
+  </si>
+  <si>
+    <t>150R</t>
   </si>
 </sst>
 </file>
@@ -665,35 +665,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -758,8 +758,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3702D4E-D911-475E-92F1-CEB23ED224C8}" name="BOM" displayName="BOM" ref="A1:F51" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:F51" xr:uid="{A3702D4E-D911-475E-92F1-CEB23ED224C8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E51">
-    <sortCondition ref="D1:D51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F51">
+    <sortCondition ref="F1:F51"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{796D7178-6F04-4724-A03F-5F2F2269C04D}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="5"/>
@@ -1119,276 +1119,272 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F2">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="F3">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>60</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="F4">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>90</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F8">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="F9">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C10" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F10">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>210</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="F11">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="F12">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="F13">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>195</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="F14">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1397,40 +1393,40 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="C15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F15">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="F16">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1439,19 +1435,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="F17">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1460,40 +1456,40 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="F18">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F19">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1502,40 +1498,40 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F20">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="F21">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1544,19 +1540,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="F22">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1565,103 +1561,103 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="F23">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C24" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="F24">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>120</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C25" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F25">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F26">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="F27">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1670,19 +1666,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="F28">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1691,31 +1687,31 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="F29">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -1724,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="F30">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1733,10 +1729,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -1745,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="F31">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
@@ -1754,388 +1750,368 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F32">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F33">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F34">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="F35">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="C36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="F36">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C37" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="F37">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="C38" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="F38">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C39" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F39">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C40" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="F40">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F41">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C42" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F42">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C43" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="F43">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="C44" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="F44">
         <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>30</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="C45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>130</v>
-      </c>
-      <c r="F45">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>132</v>
-      </c>
-      <c r="F46">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>142</v>
-      </c>
-      <c r="F47">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>141</v>
-      </c>
-      <c r="F48">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="C50" s="1">
         <v>1</v>
@@ -2144,39 +2120,32 @@
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>139</v>
-      </c>
-      <c r="F50">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
       <c r="C51" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>138</v>
-      </c>
-      <c r="F51">
-        <f>IFERROR(BOM[[#This Row],[Qty]]*15,0)</f>
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2196,339 +2165,339 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="str">
+      <c r="A1" s="9" t="str">
         <f>BOM!A18</f>
-        <v>C110,C120</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="6" t="str">
+        <v>J401</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="7" t="str">
         <f>BOM!B18</f>
-        <v>2.2uF</v>
-      </c>
-      <c r="D1" s="4" t="str">
+        <v>Conn_01x04_Socket</v>
+      </c>
+      <c r="D1" s="9" t="str">
         <f>BOM!A19</f>
-        <v>C900</v>
-      </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6" t="str">
+        <v>L410</v>
+      </c>
+      <c r="E1" s="10"/>
+      <c r="F1" s="7" t="str">
         <f>BOM!B19</f>
-        <v>220uF</v>
-      </c>
-      <c r="G1" s="4" t="str">
+        <v>Ferrite_Small</v>
+      </c>
+      <c r="G1" s="9" t="str">
         <f>BOM!A20</f>
-        <v>C901,C902</v>
-      </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="6" t="str">
+        <v>R000</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="7" t="str">
         <f>BOM!B20</f>
-        <v>10uF</v>
+        <v>0R20</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="str">
+      <c r="A2" s="4" t="str">
         <f>BOM!D18</f>
-        <v>Farnell</v>
-      </c>
-      <c r="B2" s="8" t="str">
+        <v>RS</v>
+      </c>
+      <c r="B2" s="5" t="str">
         <f>BOM!E18</f>
-        <v>8766797</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="7" t="str">
+        <v>233-9354</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="4" t="str">
         <f>BOM!D19</f>
-        <v>Farnell</v>
-      </c>
-      <c r="E2" s="8" t="str">
+        <v>RS</v>
+      </c>
+      <c r="E2" s="5" t="str">
         <f>BOM!E19</f>
-        <v>3254121</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="7" t="str">
+        <v>467-3315</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="4" t="str">
         <f>BOM!D20</f>
-        <v>Farnell</v>
-      </c>
-      <c r="H2" s="8" t="str">
+        <v>RS</v>
+      </c>
+      <c r="H2" s="5" t="str">
         <f>BOM!E20</f>
-        <v>2901339</v>
-      </c>
-      <c r="I2" s="9"/>
+        <v>846-9836</v>
+      </c>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="9" t="str">
         <f>BOM!A22</f>
-        <v>J411</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6" t="str">
+        <v>SW310</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="7" t="str">
         <f>BOM!B22</f>
-        <v>USB_B</v>
-      </c>
-      <c r="D3" s="4" t="str">
+        <v>RotaryEncoder_Switch_MP</v>
+      </c>
+      <c r="D3" s="9" t="str">
         <f>BOM!A23</f>
-        <v>Q110,Q120,Q130,Q140</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6" t="str">
+        <v>U300</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="7" t="str">
         <f>BOM!B23</f>
-        <v>IRLZ44N</v>
-      </c>
-      <c r="G3" s="4" t="str">
+        <v>74AHC595</v>
+      </c>
+      <c r="G3" s="9" t="str">
         <f>BOM!A25</f>
-        <v>U210,U220,U230,U240</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6" t="str">
+        <v>U900</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="7" t="str">
         <f>BOM!B51</f>
-        <v>Dil socket 6 pin</v>
+        <v>10nF</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="str">
+      <c r="A4" s="4" t="str">
         <f>BOM!D22</f>
-        <v>Farnell</v>
-      </c>
-      <c r="B4" s="8" t="str">
+        <v>RS</v>
+      </c>
+      <c r="B4" s="5" t="str">
         <f>BOM!E22</f>
-        <v>1076666</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="7" t="str">
+        <v>781-6830</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="4" t="str">
         <f>BOM!D23</f>
-        <v>Farnell</v>
-      </c>
-      <c r="E4" s="8" t="str">
+        <v>RS</v>
+      </c>
+      <c r="E4" s="5" t="str">
         <f>BOM!E23</f>
-        <v>8651418</v>
-      </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="7" t="str">
+        <v>100-0763</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="4" t="str">
         <f>BOM!D51</f>
         <v>RS</v>
       </c>
-      <c r="H4" s="8" t="str">
+      <c r="H4" s="5" t="str">
         <f>BOM!E51</f>
-        <v>702-0657</v>
-      </c>
-      <c r="I4" s="9"/>
+        <v>134-5708</v>
+      </c>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="9" t="str">
         <f>BOM!A26</f>
-        <v>U400</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="str">
+        <v/>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="7" t="str">
         <f>BOM!B47</f>
-        <v>Dil socket 28 pin</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6" t="str">
+        <v>MCP2221AxP</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="7" t="str">
         <f>BOM!B50</f>
-        <v>Dil socket 8 pin</v>
-      </c>
-      <c r="G5" s="4" t="str">
+        <v>470nF</v>
+      </c>
+      <c r="G5" s="9" t="str">
         <f>BOM!A27</f>
-        <v>U410</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6" t="str">
+        <v/>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="7" t="str">
         <f>BOM!B49</f>
-        <v>Dil socket 14 pin</v>
+        <v>100nF</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="str">
+      <c r="A6" s="4" t="str">
         <f>BOM!D47</f>
         <v>RS</v>
       </c>
-      <c r="B6" s="8" t="str">
+      <c r="B6" s="5" t="str">
         <f>BOM!E47</f>
-        <v>183-1570</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="7" t="str">
+        <v>171-7757</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="4" t="str">
         <f>BOM!D50</f>
         <v>RS</v>
       </c>
-      <c r="E6" s="8" t="str">
+      <c r="E6" s="5" t="str">
         <f>BOM!E50</f>
-        <v>183-1560</v>
-      </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="7" t="str">
+        <v>172-5820</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="4" t="str">
         <f>BOM!D49</f>
         <v>RS</v>
       </c>
-      <c r="H6" s="8" t="str">
+      <c r="H6" s="5" t="str">
         <f>BOM!E49</f>
-        <v>183-1562</v>
-      </c>
-      <c r="I6" s="9"/>
+        <v>135-8304</v>
+      </c>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="9" t="str">
         <f>BOM!A39</f>
-        <v>U300</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6" t="str">
+        <v>R210,R220,R230,R240</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="7" t="str">
         <f>BOM!B48</f>
-        <v>Dil socket 16 pin</v>
-      </c>
-      <c r="D7" s="4" t="str">
+        <v>1N4148</v>
+      </c>
+      <c r="D7" s="9" t="str">
         <f>BOM!A42</f>
-        <v>U900</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="7" t="str">
         <f>BOM!B42</f>
-        <v>LM317</v>
-      </c>
-      <c r="G7" s="4" t="str">
+        <v>Dil socket 6 pin</v>
+      </c>
+      <c r="G7" s="9" t="str">
         <f>BOM!A43</f>
-        <v>U901</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6" t="str">
+        <v>R211,R221,R231,R241,R251,R300,R310,R311,R312,R400,R401,R402,R410</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="7" t="str">
         <f>BOM!B43</f>
-        <v>L78L05</v>
+        <v>10k</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="4" t="str">
         <f>BOM!D48</f>
-        <v>RS</v>
-      </c>
-      <c r="B8" s="8" t="str">
+        <v>Cypax</v>
+      </c>
+      <c r="B8" s="5" t="str">
         <f>BOM!E48</f>
-        <v>183-1561</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="7" t="str">
+        <v>00.001.4148</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="4" t="str">
         <f>BOM!D42</f>
         <v>RS</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="5" t="str">
         <f>BOM!E42</f>
-        <v>168-8786</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="7" t="str">
+        <v>702-0657</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="4" t="str">
         <f>BOM!D43</f>
-        <v>RS</v>
-      </c>
-      <c r="H8" s="8" t="str">
+        <v>Cypax</v>
+      </c>
+      <c r="H8" s="5" t="str">
         <f>BOM!E43</f>
-        <v>885-5423</v>
-      </c>
-      <c r="I8" s="9"/>
+        <v xml:space="preserve">05.000.0510 </v>
+      </c>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="str">
+      <c r="A9" s="11" t="str">
         <f>BOM!A35</f>
-        <v>L410</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="6" t="s">
+        <v>C901,C902</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="11" t="str">
+        <f>BOM!A38</f>
+        <v>R112,R122,R132,R142</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="10" t="str">
-        <f>BOM!A38</f>
-        <v>SW310</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G9" s="4" t="str">
+      <c r="G9" s="9" t="str">
         <f>BOM!B46</f>
-        <v>Conn_01x06_Socket</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="12"/>
+        <v>PIC18F27Q43-xSP</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="str">
+      <c r="A10" s="4" t="str">
         <f>BOM!D34</f>
-        <v>RS</v>
-      </c>
-      <c r="B10" s="8" t="str">
+        <v>Cypax</v>
+      </c>
+      <c r="B10" s="5" t="str">
         <f>BOM!E34</f>
-        <v>233-9354</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="7" t="str">
+        <v>05.000.0433</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="4" t="str">
         <f>BOM!D38</f>
-        <v>RS</v>
-      </c>
-      <c r="E10" s="8" t="str">
+        <v>Cypax</v>
+      </c>
+      <c r="E10" s="5" t="str">
         <f>BOM!E38</f>
-        <v>781-6830</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="7" t="str">
+        <v>05.000.0315</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="4" t="str">
         <f>BOM!D46</f>
-        <v>RS</v>
-      </c>
-      <c r="H10" s="8" t="str">
+        <v>Farnell</v>
+      </c>
+      <c r="H10" s="5" t="str">
         <f>BOM!E46</f>
-        <v>252-5144</v>
-      </c>
-      <c r="I10" s="13"/>
+        <v>3052751</v>
+      </c>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="str">
+      <c r="A11" s="9" t="str">
         <f>BOM!B32</f>
-        <v>Conn_01x02_Socket</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="4" t="str">
+        <v>47k</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="9" t="str">
         <f>BOM!A33</f>
-        <v>J400</v>
-      </c>
-      <c r="E11" s="5"/>
+        <v>R131,R141</v>
+      </c>
+      <c r="E11" s="10"/>
       <c r="F11" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="9" t="str">
+        <f>BOM!A34</f>
+        <v>R900,R903</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="G11" s="4" t="str">
-        <f>BOM!A34</f>
-        <v>J401</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="14" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="12" spans="1:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="str">
+      <c r="A12" s="4" t="str">
         <f>BOM!D32</f>
-        <v>RS</v>
-      </c>
-      <c r="B12" s="8" t="str">
+        <v>Cypax</v>
+      </c>
+      <c r="B12" s="5" t="str">
         <f>BOM!E32</f>
-        <v>252-5139</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="7" t="str">
+        <v>05.000.0547</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="4" t="str">
         <f>BOM!D33</f>
-        <v>RS</v>
-      </c>
-      <c r="E12" s="8" t="str">
+        <v>Cypax</v>
+      </c>
+      <c r="E12" s="5" t="str">
         <f>BOM!E33</f>
-        <v>233-9362</v>
+        <v>05.000.0627</v>
       </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="7" t="str">
+      <c r="G12" s="4" t="str">
         <f>BOM!D34</f>
-        <v>RS</v>
-      </c>
-      <c r="H12" s="8" t="str">
+        <v>Cypax</v>
+      </c>
+      <c r="H12" s="5" t="str">
         <f>BOM!E34</f>
-        <v>233-9354</v>
+        <v>05.000.0433</v>
       </c>
       <c r="I12" s="15"/>
     </row>
@@ -2554,11 +2523,6 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:C4"/>
@@ -2566,12 +2530,17 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
